--- a/product_selector_out/STM32L0x2.xlsx
+++ b/product_selector_out/STM32L0x2.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -85,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -99,6 +104,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9019,9 +9025,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX12" s="7" t="inlineStr">
@@ -9346,9 +9352,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX13" s="7" t="inlineStr">
@@ -9673,9 +9679,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX14" s="7" t="inlineStr">
@@ -10000,9 +10006,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX15" s="7" t="inlineStr">
@@ -10327,9 +10333,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX16" s="7" t="inlineStr">
@@ -10654,9 +10660,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX17" s="7" t="inlineStr">
@@ -10981,9 +10987,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX18" s="7" t="inlineStr">
@@ -11308,9 +11314,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX19" s="7" t="inlineStr">
@@ -11635,9 +11641,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX20" s="7" t="inlineStr">
@@ -11962,9 +11968,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX21" s="7" t="inlineStr">
@@ -12289,9 +12295,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX22" s="7" t="inlineStr">
@@ -12616,9 +12622,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX23" s="7" t="inlineStr">
@@ -12943,9 +12949,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX24" s="7" t="inlineStr">
@@ -13270,9 +13276,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX25" s="7" t="inlineStr">
@@ -13597,9 +13603,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX26" s="7" t="inlineStr">
@@ -13924,9 +13930,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX27" s="7" t="inlineStr">
@@ -14251,9 +14257,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX28" s="7" t="inlineStr">
@@ -14578,9 +14584,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX29" s="7" t="inlineStr">
@@ -14905,9 +14911,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX30" s="7" t="inlineStr">
@@ -15232,9 +15238,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX31" s="7" t="inlineStr">
@@ -15559,9 +15565,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX32" s="7" t="inlineStr">
@@ -15886,9 +15892,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX33" s="7" t="inlineStr">
@@ -15987,7 +15993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16018,7 +16024,490 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STM32L072KZ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STM32L072KB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STM32L062C8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32L082CZ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32L072V8</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32L082KZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32L072CZ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32L082KB</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32L072RZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32L062K8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32L072VB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32L072RB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32L052T8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32L072CB</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32L052T6</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32L072VZ</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32L052K8</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32L052C8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32L052C6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32L052R6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32L052R8</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32L052K6</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32L0x2.xlsx
+++ b/product_selector_out/STM32L0x2.xlsx
@@ -2949,7 +2949,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l082cz.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10440,9 +10440,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -10660,14 +10660,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY17" s="6" t="inlineStr">
@@ -10740,9 +10740,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -15993,7 +15993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16137,7 +16137,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32L082KZ</t>
+          <t>STM32L072CZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -16152,14 +16152,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32L072CZ</t>
+          <t>STM32L082KB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -16174,14 +16174,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 23. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32L082KB</t>
+          <t>STM32L072RZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -16196,14 +16196,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32L072RZ</t>
+          <t>STM32L062K8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -16218,14 +16218,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32L062K8</t>
+          <t>STM32L072VB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -16240,14 +16240,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32L072VB</t>
+          <t>STM32L072RB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -16269,7 +16269,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32L072RB</t>
+          <t>STM32L052T8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -16284,14 +16284,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32L052T8</t>
+          <t>STM32L072CB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -16306,14 +16306,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32L072CB</t>
+          <t>STM32L052T6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -16328,14 +16328,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32L052T6</t>
+          <t>STM32L072VZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -16350,14 +16350,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32L072VZ</t>
+          <t>STM32L052K8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -16372,14 +16372,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32L052K8</t>
+          <t>STM32L052C8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -16401,7 +16401,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32L052C8</t>
+          <t>STM32L052C6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -16423,7 +16423,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32L052C6</t>
+          <t>STM32L052R6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -16445,7 +16445,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32L052R6</t>
+          <t>STM32L052R8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -16467,7 +16467,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L052R8</t>
+          <t>STM32L052K6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -16481,28 +16481,6 @@
         </is>
       </c>
       <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32L052K6</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
         <is>
           <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>

--- a/product_selector_out/STM32L0x2.xlsx
+++ b/product_selector_out/STM32L0x2.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM33"/>
+  <dimension ref="A1:BN33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.3671875" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l062c8.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l082cz.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -2952,6 +2984,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l082cz.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l062c8.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l072cb.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
@@ -7854,6 +7961,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
@@ -8181,12 +8293,17 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l052c6.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -8207,16 +8324,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -8229,6 +8344,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -8248,7 +8364,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -8287,7 +8405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM33"/>
+  <dimension ref="A1:BN33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8355,6 +8473,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8688,6 +8807,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -8783,6 +8907,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -9105,7 +9230,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9432,7 +9562,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9759,7 +9894,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10086,7 +10226,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10413,7 +10558,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10745,6 +10895,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -11067,7 +11222,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11394,7 +11554,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11721,7 +11886,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12048,7 +12218,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12375,7 +12550,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12702,7 +12882,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13029,7 +13214,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13356,7 +13546,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13683,7 +13878,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14010,7 +14210,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14337,7 +14542,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14664,7 +14874,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14991,7 +15206,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15318,7 +15538,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15645,7 +15870,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15972,7 +16202,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15980,8 +16215,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
